--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104646_W21.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104646_W21.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5998</v>
+        <v>6.5009</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2156</v>
+        <v>5.7852</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3842</v>
+        <v>0.7157</v>
       </c>
       <c r="G2" t="n">
-        <v>5.4633</v>
+        <v>5.4684</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6507</v>
+        <v>3.6477</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8126</v>
+        <v>1.8207</v>
       </c>
       <c r="J2" t="n">
-        <v>6.1598</v>
+        <v>6.1239</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4087</v>
+        <v>4.3814</v>
       </c>
       <c r="L2" t="n">
-        <v>1.7512</v>
+        <v>1.7425</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6965</v>
+        <v>-0.6555</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7579</v>
+        <v>-0.7337</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0614</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.09039999999999999</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5172</v>
+        <v>0.097</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4267</v>
+        <v>0.7079</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1199</v>
+        <v>5.1049</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2006</v>
+        <v>4.2981</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9193</v>
+        <v>0.8069</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2808</v>
+        <v>-0.2715</v>
       </c>
       <c r="H3" t="n">
-        <v>1.02</v>
+        <v>1.0305</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.3008</v>
+        <v>-1.302</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3752</v>
+        <v>1.346</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7938</v>
+        <v>1.7786</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.4186</v>
+        <v>-0.4326</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.656</v>
+        <v>-1.6175</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7738</v>
+        <v>-0.7481</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8822</v>
+        <v>-0.8694</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5429</v>
+        <v>0.4542</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.5303</v>
+        <v>-0.3768</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9875</v>
+        <v>0.831</v>
       </c>
       <c r="V3" t="n">
-        <v>5.6241</v>
+        <v>5.6051</v>
       </c>
       <c r="W3" t="n">
-        <v>5.6241</v>
+        <v>5.6051</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1647</v>
+        <v>2.6538</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7473</v>
+        <v>2.1347</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4174</v>
+        <v>0.5191</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.955</v>
+        <v>-0.9466</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3016</v>
+        <v>-1.2984</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3466</v>
+        <v>0.3518</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.2125</v>
+        <v>-1.2342</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5754</v>
+        <v>-0.5935</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2575</v>
+        <v>0.2876</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7261</v>
+        <v>-0.7048</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9837</v>
+        <v>0.9925</v>
       </c>
       <c r="P4" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5873</v>
+        <v>-0.1021</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0253</v>
+        <v>-0.602</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4379</v>
+        <v>0.4999</v>
       </c>
       <c r="V4" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="W4" t="n">
-        <v>3.9851</v>
+        <v>3.9709</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="5">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4257</v>
+        <v>1.3285</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2649</v>
+        <v>0.7952</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1608</v>
+        <v>0.5333</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6187</v>
+        <v>1.6361</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5178</v>
+        <v>0.5306</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1009</v>
+        <v>1.1055</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7721</v>
+        <v>1.7617</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6927</v>
+        <v>0.6895</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0795</v>
+        <v>1.0722</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1534</v>
+        <v>-0.1255</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1749</v>
+        <v>-0.1588</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0214</v>
+        <v>0.0333</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S5" t="n">
-        <v>0.529</v>
+        <v>0.4239</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6684</v>
+        <v>0.2203</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1394</v>
+        <v>0.2036</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. JOKSIMOVIC</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8113</v>
+        <v>0.6979</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1263</v>
+        <v>3.1523</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9376</v>
+        <v>-2.4544</v>
       </c>
       <c r="G6" t="n">
-        <v>0.469</v>
+        <v>3.0197</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6103</v>
+        <v>1.8923</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1414</v>
+        <v>1.1274</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7084</v>
+        <v>2.9902</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0448</v>
+        <v>2.2236</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6636</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2395</v>
+        <v>0.0296</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5655</v>
+        <v>-0.3312</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.805</v>
+        <v>0.3608</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0229</v>
+        <v>-0.281</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2994</v>
+        <v>0.0044</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7234</v>
+        <v>-0.2854</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-2.7237</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>S. JOKSIMOVIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2363</v>
+        <v>0.5715</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5649</v>
+        <v>-0.3186</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.8012</v>
+        <v>0.8901</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0186</v>
+        <v>0.4577</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8858</v>
+        <v>0.6117</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1328</v>
+        <v>-0.154</v>
       </c>
       <c r="J7" t="n">
-        <v>3.0121</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>2.2339</v>
+        <v>0.0377</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7782</v>
+        <v>0.6473</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0065</v>
+        <v>-0.2273</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.348</v>
+        <v>0.574</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3546</v>
+        <v>-0.8012</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2037</v>
+        <v>0.7967</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6079</v>
+        <v>0.1345</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5958</v>
+        <v>0.6622</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.7317</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.8924</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8305</v>
+        <v>-0.7013</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0485</v>
+        <v>-1.0542</v>
       </c>
       <c r="F8" t="n">
-        <v>0.218</v>
+        <v>0.3529</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3424</v>
+        <v>-0.3371</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0678</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2944</v>
+        <v>0.293</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2944</v>
+        <v>0.293</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6368</v>
+        <v>-0.6301</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3622</v>
+        <v>-0.3592</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1252</v>
+        <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2087</v>
+        <v>-0.2091</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0835</v>
+        <v>0.2091</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3767</v>
+        <v>-1.3385</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7107</v>
+        <v>-2.0259</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3339</v>
+        <v>0.6874</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.5283</v>
+        <v>-1.1493</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9423</v>
+        <v>0.1975</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.586</v>
+        <v>-1.3469</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.3277</v>
+        <v>-0.7504</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.603</v>
+        <v>0.4719</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.7247</v>
+        <v>-1.2223</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2007</v>
+        <v>-0.399</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3393</v>
+        <v>-0.2744</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1387</v>
+        <v>-0.1246</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1342</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0174</v>
+        <v>1.0385</v>
       </c>
       <c r="T9" t="n">
-        <v>0.617</v>
+        <v>-0.0887</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4004</v>
+        <v>1.1272</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4217</v>
+        <v>-2.1809</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4975</v>
+        <v>-2.4177</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0758</v>
+        <v>0.2368</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1549</v>
+        <v>-3.5257</v>
       </c>
       <c r="H10" t="n">
-        <v>0.186</v>
+        <v>-1.9361</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3408</v>
+        <v>-1.5896</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.717</v>
+        <v>-2.3499</v>
       </c>
       <c r="K10" t="n">
-        <v>0.488</v>
+        <v>-0.614</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.205</v>
+        <v>-1.7359</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4379</v>
+        <v>-1.1758</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.302</v>
+        <v>-1.3221</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1359</v>
+        <v>0.1463</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9599</v>
+        <v>0.2067</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6049</v>
+        <v>-0.0678</v>
       </c>
       <c r="U10" t="n">
-        <v>1.5648</v>
+        <v>0.2744</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.536</v>
+        <v>-4.5081</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4985</v>
+        <v>-5.1551</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9625</v>
+        <v>0.647</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.0648</v>
+        <v>-6.0817</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.0358</v>
+        <v>-5.043</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.029</v>
+        <v>-1.0387</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.8373</v>
+        <v>-4.8783</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.0428</v>
+        <v>-4.0656</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7945</v>
+        <v>-0.8126</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2275</v>
+        <v>-1.2034</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.993</v>
+        <v>-0.9774</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>2.0751</v>
+        <v>1.1183</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4729</v>
+        <v>0.8613</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6021</v>
+        <v>0.257</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.720199999999998</v>
+        <v>8.128699999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>4.111800000000001</v>
+        <v>5.194</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6083</v>
+        <v>2.9348</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.756599999999999</v>
+        <v>-1.73</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4769000000000005</v>
+        <v>-0.4333999999999998</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2796</v>
+        <v>-1.2968</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2275</v>
+        <v>3.986999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>4.735099999999999</v>
+        <v>4.602599999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5074000000000001</v>
+        <v>-0.6155000000000002</v>
       </c>
       <c r="M12" t="n">
-        <v>-5.9843</v>
+        <v>-5.7169</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.2117</v>
+        <v>-5.0357</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7723</v>
+        <v>-0.6810999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q12" t="n">
-        <v>-11.3417</v>
+        <v>-11.3817</v>
       </c>
       <c r="R12" t="n">
-        <v>10.2075</v>
+        <v>10.2435</v>
       </c>
       <c r="S12" t="n">
-        <v>3.0548</v>
+        <v>4.4601</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.436599999999999</v>
+        <v>-0.02690000000000003</v>
       </c>
       <c r="U12" t="n">
-        <v>4.4911</v>
+        <v>4.486899999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>6.556099999999999</v>
+        <v>6.536799999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>12.6624</v>
+        <v>12.6153</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.1063</v>
+        <v>-6.0784</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.3768</v>
+        <v>3.4322</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3114</v>
+        <v>2.9829</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0654</v>
+        <v>0.4494</v>
       </c>
       <c r="G13" t="n">
-        <v>3.9503</v>
+        <v>3.9514</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8685</v>
+        <v>1.8751</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0817</v>
+        <v>2.0763</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5355</v>
+        <v>3.5058</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9092</v>
+        <v>2.8958</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6263</v>
+        <v>0.61</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4148</v>
+        <v>0.4456</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0407</v>
+        <v>-1.0207</v>
       </c>
       <c r="O13" t="n">
-        <v>1.4555</v>
+        <v>1.4663</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2539</v>
+        <v>-0.202</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9557</v>
+        <v>-0.2466</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2982</v>
+        <v>0.0446</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.307</v>
+        <v>2.0683</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3768</v>
+        <v>3.3604</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0698</v>
+        <v>-1.2921</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9058</v>
+        <v>1.913</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.7151</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1915</v>
+        <v>1.1979</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2429</v>
+        <v>3.2311</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9741</v>
+        <v>1.965</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3371</v>
+        <v>-1.318</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2599</v>
+        <v>-1.2499</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S14" t="n">
-        <v>0.199</v>
+        <v>-0.0512</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0393</v>
+        <v>0.0414</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1597</v>
+        <v>-0.0926</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. AGADA</t>
+          <t>A. DIAGNE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7477</v>
+        <v>0.8081</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1291</v>
+        <v>1.6859</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8768</v>
+        <v>-0.8778</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7338</v>
+        <v>2.0728</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9135</v>
+        <v>1.9906</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.6473</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.8357</v>
+        <v>2.2436</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8516</v>
+        <v>2.2063</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.6874</v>
+        <v>0.0372</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1019</v>
+        <v>-0.1708</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0619</v>
+        <v>-0.2157</v>
       </c>
       <c r="O15" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0278</v>
+        <v>-0.4727</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1603</v>
+        <v>-0.5576</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1325</v>
+        <v>0.0849</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5463</v>
+        <v>-1.2472</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. DIAGNE</t>
+          <t>C. AGADA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.5929</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6974</v>
+        <v>-0.3946</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0516</v>
+        <v>0.9875</v>
       </c>
       <c r="G16" t="n">
-        <v>2.073</v>
+        <v>-0.7486</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9957</v>
+        <v>0.9052</v>
       </c>
       <c r="I16" t="n">
-        <v>0.07729999999999999</v>
+        <v>-1.6538</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2539</v>
+        <v>-0.8648</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2165</v>
+        <v>0.8339</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0373</v>
+        <v>-1.6987</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1808</v>
+        <v>0.1162</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2209</v>
+        <v>0.0713</v>
       </c>
       <c r="O16" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6276</v>
+        <v>-0.1138</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5565</v>
+        <v>-0.0746</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0711</v>
+        <v>-0.0392</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2534</v>
+        <v>0.5447</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5098</v>
+        <v>-0.1184</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0427</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5329</v>
+        <v>-0.9949</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0551</v>
+        <v>0.0396</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.1973</v>
+        <v>-2.2189</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2524</v>
+        <v>2.2585</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.5099</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.047</v>
+        <v>-1.0836</v>
       </c>
       <c r="L17" t="n">
-        <v>1.6019</v>
+        <v>1.5935</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4998</v>
+        <v>-0.4703</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1503</v>
+        <v>-1.1353</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6505</v>
+        <v>0.665</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>0.64</v>
+        <v>0.021</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.378</v>
+        <v>-0.4952</v>
       </c>
       <c r="U17" t="n">
-        <v>1.018</v>
+        <v>0.5162</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. JIMENEZ</t>
+          <t>J. SHURNA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0436</v>
+        <v>-0.6742</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0732</v>
+        <v>-0.9213</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1168</v>
+        <v>0.247</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7302999999999999</v>
+        <v>-0.666</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1573</v>
+        <v>-1.2439</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5731000000000001</v>
+        <v>0.5778</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3654</v>
+        <v>-0.31</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.44</v>
+        <v>-1.1139</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0746</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3649</v>
+        <v>-0.356</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2828</v>
+        <v>-0.13</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.226</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3257</v>
+        <v>-0.0569</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4386</v>
+        <v>-0.3836</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1128</v>
+        <v>0.3267</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.082</v>
+        <v>-0.831</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9864000000000001</v>
+        <v>-0.8811</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0956</v>
+        <v>0.0501</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2033</v>
+        <v>-1.197</v>
       </c>
       <c r="H19" t="n">
-        <v>0.492</v>
+        <v>0.4966</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6953</v>
+        <v>-1.6936</v>
       </c>
       <c r="J19" t="n">
-        <v>0.057</v>
+        <v>0.046</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3983</v>
+        <v>0.3964</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3413</v>
+        <v>-0.3505</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2603</v>
+        <v>-1.243</v>
       </c>
       <c r="N19" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9448</v>
+        <v>-0.7039</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0434</v>
+        <v>-0.9271</v>
       </c>
       <c r="U19" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.2232</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SHURNA</t>
+          <t>M. JIMENEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3355</v>
+        <v>-1.2948</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4903</v>
+        <v>-0.2846</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1548</v>
+        <v>-1.0102</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6672</v>
+        <v>-0.7268</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2482</v>
+        <v>-0.1579</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5810999999999999</v>
+        <v>-0.5688</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2896</v>
+        <v>-0.3704</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.1052</v>
+        <v>-0.4449</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8156</v>
+        <v>0.0745</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3776</v>
+        <v>-0.3563</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1431</v>
+        <v>0.287</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2345</v>
+        <v>-0.6433</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7098</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9739</v>
+        <v>0.0858</v>
       </c>
       <c r="U20" t="n">
-        <v>0.264</v>
+        <v>-0.0196</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3708</v>
+        <v>-2.0734</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9748</v>
+        <v>-1.7649</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.396</v>
+        <v>-0.3086</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2319</v>
+        <v>-0.2268</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1385</v>
+        <v>0.1379</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3705</v>
+        <v>-0.3647</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1797</v>
+        <v>1.1622</v>
       </c>
       <c r="K21" t="n">
-        <v>1.257</v>
+        <v>1.2443</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4116</v>
+        <v>-1.389</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1185</v>
+        <v>-1.1064</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5511</v>
+        <v>-0.2532</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8861</v>
+        <v>-0.6506999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3351</v>
+        <v>0.3975</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. BATEMON</t>
+          <t>M. SANZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4184</v>
+        <v>-2.2181</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6622</v>
+        <v>-4.1881</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7562</v>
+        <v>1.9701</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.1385</v>
+        <v>0.5057</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.2535</v>
+        <v>0.3298</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.885</v>
+        <v>0.1759</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.191</v>
+        <v>-0.629</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2446</v>
+        <v>0.0862</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.9464</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9475</v>
+        <v>1.1347</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0089</v>
+        <v>0.2437</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0614</v>
+        <v>0.8911</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.4952</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3759</v>
+        <v>-0.5841</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1996</v>
+        <v>-0.5089</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1763</v>
+        <v>-0.0752</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4783</v>
+        <v>-0.7739</v>
       </c>
       <c r="W22" t="n">
-        <v>3.8243</v>
+        <v>-0.7739</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. SANZ</t>
+          <t>C. KRUTWIG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4627</v>
+        <v>-2.6921</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2907</v>
+        <v>-1.9517</v>
       </c>
       <c r="F23" t="n">
-        <v>1.8281</v>
+        <v>-0.7403999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4949</v>
+        <v>-0.0173</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3216</v>
+        <v>-0.1174</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1733</v>
+        <v>0.1001</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6251</v>
+        <v>-0.5508</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0866</v>
+        <v>-0.6625</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7117</v>
+        <v>0.1117</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1201</v>
+        <v>0.5335</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2351</v>
+        <v>0.5451</v>
       </c>
       <c r="O23" t="n">
-        <v>0.885</v>
+        <v>-0.0116</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.361</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8254</v>
+        <v>0.1871</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6261</v>
+        <v>-0.2627</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1993</v>
+        <v>0.4498</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.7712</v>
+        <v>-2.1789</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C. KRUTWIG</t>
+          <t>J. BATEMON</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.5941</v>
+        <v>-2.9445</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5762</v>
+        <v>-1.4542</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0179</v>
+        <v>-1.4903</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0177</v>
+        <v>-3.1701</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.111</v>
+        <v>-2.279</v>
       </c>
       <c r="I24" t="n">
-        <v>0.09329999999999999</v>
+        <v>-0.8911</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-2.2565</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6447000000000001</v>
+        <v>-1.2872</v>
       </c>
       <c r="L24" t="n">
-        <v>0.112</v>
+        <v>-0.9693000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5151</v>
+        <v>-0.9136</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5337</v>
+        <v>-0.9918</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0186</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6805</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-2.5039</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2894</v>
+        <v>-0.1127</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0907</v>
+        <v>-0.5069</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1987</v>
+        <v>0.3942</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.1853</v>
+        <v>1.4764</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.8132</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1853</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.7201</v>
+        <v>-5.945</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.608200000000001</v>
+        <v>-2.934800000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.1117</v>
+        <v>-3.0102</v>
       </c>
       <c r="G25" t="n">
-        <v>1.7564</v>
+        <v>1.729899999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4767000000000011</v>
+        <v>0.4331999999999998</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2794</v>
+        <v>1.2966</v>
       </c>
       <c r="J25" t="n">
-        <v>5.9843</v>
+        <v>5.7171</v>
       </c>
       <c r="K25" t="n">
-        <v>5.211799999999999</v>
+        <v>5.0358</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7723999999999996</v>
+        <v>0.6810999999999998</v>
       </c>
       <c r="M25" t="n">
-        <v>-4.2277</v>
+        <v>-3.987</v>
       </c>
       <c r="N25" t="n">
-        <v>-4.7351</v>
+        <v>-4.6025</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5073000000000001</v>
+        <v>0.6156000000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>1.134200000000001</v>
+        <v>1.1382</v>
       </c>
       <c r="Q25" t="n">
-        <v>-10.2074</v>
+        <v>-10.2433</v>
       </c>
       <c r="R25" t="n">
-        <v>11.3417</v>
+        <v>11.3817</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.0548</v>
+        <v>-2.2762</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.4912</v>
+        <v>-4.486700000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4365</v>
+        <v>2.2105</v>
       </c>
       <c r="V25" t="n">
-        <v>-6.5561</v>
+        <v>-6.536799999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>6.106199999999999</v>
+        <v>6.0785</v>
       </c>
       <c r="X25" t="n">
-        <v>-12.6623</v>
+        <v>-12.6151</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104646_W21.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104646_W21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104646_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104646_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104646_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104646_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104646_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104646_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104646_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104646_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104646_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104646_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-6.0784</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104646_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104646_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104646_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104646_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104646_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104646_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104646_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104646_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104646_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104646_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104646_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104646_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-12.6151</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
